--- a/plantillas/9.xlsx
+++ b/plantillas/9.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$3</definedName>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/9.xlsx
+++ b/plantillas/9.xlsx
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/9.xlsx
+++ b/plantillas/9.xlsx
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
